--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104488_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104488_W4.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2899</v>
+        <v>4.799</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9477</v>
+        <v>3.3157</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6578000000000001</v>
+        <v>1.4833</v>
       </c>
       <c r="G2" t="n">
-        <v>1.692</v>
+        <v>2.7053</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2251</v>
+        <v>1.6999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.533</v>
+        <v>1.0054</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0477</v>
+        <v>2.2601</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2268</v>
+        <v>1.672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.821</v>
+        <v>0.5881</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3557</v>
+        <v>0.4452</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0017</v>
+        <v>0.028</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.354</v>
+        <v>0.4173</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7645</v>
+        <v>-0.986</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6635</v>
+        <v>-0.5786</v>
       </c>
       <c r="U2" t="n">
-        <v>0.101</v>
+        <v>-0.4074</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6481</v>
+        <v>1.2586</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7317</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.3757</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2549</v>
+        <v>2.6192</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0784</v>
+        <v>3.6872</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1766</v>
+        <v>-1.0681</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7015</v>
+        <v>1.6992</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6939</v>
+        <v>2.2231</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0076</v>
+        <v>-0.5239</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2741</v>
+        <v>3.0288</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6797</v>
+        <v>2.2096</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5944</v>
+        <v>0.8192</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4274</v>
+        <v>-1.3296</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0142</v>
+        <v>0.0135</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4132</v>
+        <v>-1.3432</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.521</v>
+        <v>0.0977</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8347</v>
+        <v>0.4387</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6863</v>
+        <v>-0.341</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2598</v>
+        <v>2.6433</v>
       </c>
       <c r="W3" t="n">
-        <v>1.639</v>
+        <v>2.7237</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3793</v>
+        <v>-0.0804</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3376</v>
+        <v>2.3314</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0427</v>
+        <v>1.8511</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2949</v>
+        <v>0.4803</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2653</v>
+        <v>0.2711</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4212</v>
+        <v>0.4263</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5197</v>
+        <v>1.5022</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2543</v>
+        <v>-1.231</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6276</v>
+        <v>-0.6399</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1179</v>
+        <v>-0.2837</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="V4" t="n">
-        <v>1.112</v>
+        <v>1.1067</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2442</v>
+        <v>0.2465</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>J. SASTRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9178</v>
+        <v>2.0989</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0302</v>
+        <v>1.8121</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9481</v>
+        <v>0.2867</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2327</v>
+        <v>2.7677</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3262</v>
+        <v>0.7286</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5588</v>
+        <v>2.039</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5262</v>
+        <v>2.5208</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5208</v>
+        <v>0.4137</v>
       </c>
       <c r="L5" t="n">
-        <v>2.047</v>
+        <v>2.1072</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7064</v>
+        <v>0.2468</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1946</v>
+        <v>0.3149</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5118</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7685</v>
+        <v>-0.8046</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5565</v>
+        <v>-0.4811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.212</v>
+        <v>-0.3235</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.23</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8484</v>
+        <v>2.0945</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2812</v>
+        <v>2.1166</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4328</v>
+        <v>-0.0221</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0607</v>
+        <v>4.0341</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1317</v>
+        <v>0.1076</v>
       </c>
       <c r="I6" t="n">
-        <v>3.929</v>
+        <v>3.9265</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7105</v>
+        <v>3.657</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3543</v>
+        <v>-0.3942</v>
       </c>
       <c r="L6" t="n">
-        <v>4.0648</v>
+        <v>4.0511</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3502</v>
+        <v>0.3771</v>
       </c>
       <c r="N6" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0047</v>
+        <v>-0.7292</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1875</v>
+        <v>-0.2837</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8172</v>
+        <v>-0.4455</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.527</v>
+        <v>-0.5275</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7804</v>
+        <v>-1.7747</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SASTRE</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8093</v>
+        <v>1.9359</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3366</v>
+        <v>0.2541</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4727</v>
+        <v>1.6818</v>
       </c>
       <c r="G7" t="n">
-        <v>2.757</v>
+        <v>2.2295</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7126</v>
+        <v>-0.3219</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0444</v>
+        <v>2.5514</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5372</v>
+        <v>0.5051</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4156</v>
+        <v>-1.5276</v>
       </c>
       <c r="L7" t="n">
-        <v>2.1216</v>
+        <v>2.0327</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2197</v>
+        <v>1.7244</v>
       </c>
       <c r="N7" t="n">
-        <v>0.297</v>
+        <v>1.2057</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0772</v>
+        <v>0.5187</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0746</v>
+        <v>-0.7488</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9739</v>
+        <v>-0.251</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1007</v>
+        <v>-0.4978</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2341</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2603</v>
+        <v>1.7368</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3332</v>
+        <v>1.8694</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1326</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5745</v>
+        <v>1.571</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.182</v>
+        <v>-0.1728</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7565</v>
+        <v>1.7438</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0984</v>
+        <v>2.0717</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9324</v>
+        <v>1.9133</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5239</v>
+        <v>-0.5007</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8157</v>
+        <v>-0.3494</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>-0.2023</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0505</v>
+        <v>-0.1471</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0863</v>
+        <v>-1.0782</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0863</v>
+        <v>-1.0782</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.103</v>
+        <v>0.3418</v>
       </c>
       <c r="E9" t="n">
-        <v>2.503</v>
+        <v>2.7873</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4</v>
+        <v>-2.4455</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4543</v>
+        <v>1.4544</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1269</v>
+        <v>0.1318</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3274</v>
+        <v>1.3226</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1241</v>
+        <v>4.1068</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4027</v>
+        <v>1.3962</v>
       </c>
       <c r="L9" t="n">
-        <v>2.7214</v>
+        <v>2.7106</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6698</v>
+        <v>-2.6524</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.6573</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4869</v>
+        <v>-0.1813</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4107</v>
+        <v>-0.476</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1322</v>
+        <v>0.1011</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3077</v>
+        <v>0.5264</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4399</v>
+        <v>-0.4252</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6945</v>
+        <v>-2.6893</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5888</v>
+        <v>-0.5861</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1057</v>
+        <v>-2.1032</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3942</v>
+        <v>-1.4014</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3003</v>
+        <v>-1.2879</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3145</v>
+        <v>-0.079</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1028</v>
+        <v>0.1024</v>
       </c>
       <c r="V10" t="n">
-        <v>2.4232</v>
+        <v>2.4141</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="11">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2327</v>
+        <v>-0.1995</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0645</v>
+        <v>-0.0649</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1682</v>
+        <v>-0.1345</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3574</v>
+        <v>0.3615</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3892</v>
+        <v>0.3903</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5901</v>
+        <v>-0.5609</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4509</v>
+        <v>-0.4215</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2049</v>
+        <v>-1.5664</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4134</v>
+        <v>0.769</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6183</v>
+        <v>-2.3354</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2988</v>
+        <v>-0.2914</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0877</v>
+        <v>0.1053</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3866</v>
+        <v>-0.3967</v>
       </c>
       <c r="J12" t="n">
-        <v>0.225</v>
+        <v>0.2094</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1038</v>
+        <v>0.0887</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5239</v>
+        <v>-0.5007</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0137</v>
+        <v>-1.3936</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9043</v>
+        <v>-0.5298</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1094</v>
+        <v>-0.8637</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.2514</v>
+        <v>16.2927</v>
       </c>
       <c r="E13" t="n">
-        <v>18.1492</v>
+        <v>18.924</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8976</v>
+        <v>-2.6313</v>
       </c>
       <c r="G13" t="n">
-        <v>14.1021</v>
+        <v>14.1131</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6932</v>
+        <v>3.7315</v>
       </c>
       <c r="I13" t="n">
-        <v>10.4088</v>
+        <v>10.3815</v>
       </c>
       <c r="J13" t="n">
-        <v>18.7433</v>
+        <v>18.535</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6308</v>
+        <v>3.5242</v>
       </c>
       <c r="L13" t="n">
-        <v>15.1127</v>
+        <v>15.0107</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.6414</v>
+        <v>-4.4218</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06259999999999979</v>
+        <v>0.2075000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.7041</v>
+        <v>-4.6294</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6708</v>
+        <v>5.6908</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.805000000000001</v>
+        <v>-6.8288</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.863599999999999</v>
+        <v>-6.851000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.7199</v>
+        <v>-2.6735</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.1435</v>
+        <v>-4.1773</v>
       </c>
       <c r="V13" t="n">
-        <v>3.3423</v>
+        <v>3.339799999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>9.930700000000002</v>
+        <v>9.891599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.5885</v>
+        <v>-6.5518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>X. CASTANEDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6795</v>
+        <v>2.1858</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4688</v>
+        <v>1.699</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7893</v>
+        <v>0.4867</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7794</v>
+        <v>-0.0047</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3609</v>
+        <v>-1.8267</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.1404</v>
+        <v>1.822</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1335</v>
+        <v>0.3962</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1735</v>
+        <v>-0.907</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.04</v>
+        <v>1.3033</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.913</v>
+        <v>-0.4009</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1874</v>
+        <v>-0.9196</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1003</v>
+        <v>0.5187</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8446</v>
+        <v>0.2799</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5356</v>
+        <v>0.0556</v>
       </c>
       <c r="U14" t="n">
-        <v>1.309</v>
+        <v>0.2243</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>1.2472</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. CASTANEDA</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4239</v>
+        <v>0.5661</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2447</v>
+        <v>2.9239</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1792</v>
+        <v>-2.3579</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0089</v>
+        <v>-0.8751</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8268</v>
+        <v>-0.9881</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8179</v>
+        <v>0.113</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4087</v>
+        <v>1.2995</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8974</v>
+        <v>-1.2173</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>2.5168</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4176</v>
+        <v>-2.1745</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9294</v>
+        <v>0.2292</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5118</v>
+        <v>-2.4037</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4745</v>
+        <v>0.4411</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4174</v>
+        <v>0.2179</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0572</v>
+        <v>0.2232</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4119</v>
+        <v>0.1133</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2676</v>
+        <v>1.4338</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8556</v>
+        <v>-1.3205</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5893</v>
+        <v>-0.7851</v>
       </c>
       <c r="H16" t="n">
-        <v>0.293</v>
+        <v>1.3477</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8823</v>
+        <v>-2.1328</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4782</v>
+        <v>1.1025</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2224</v>
+        <v>1.1474</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2558</v>
+        <v>-0.0449</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0675</v>
+        <v>-1.8876</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9294</v>
+        <v>0.2003</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1381</v>
+        <v>-2.0879</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0939</v>
+        <v>2.2853</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0162</v>
+        <v>1.5393</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0311</v>
+        <v>-0.2007</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4782</v>
+        <v>1.5385</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5093</v>
+        <v>-1.7392</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8726</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9899</v>
+        <v>0.2902</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1172</v>
+        <v>-0.8834</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3231</v>
+        <v>1.4552</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2091</v>
+        <v>1.2098</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5321</v>
+        <v>0.2453</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1957</v>
+        <v>-2.0483</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2192</v>
+        <v>-0.9196</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.4149</v>
+        <v>-1.1287</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1585</v>
+        <v>0.4819</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2571</v>
+        <v>0.311</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.171</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6421</v>
+        <v>-1.2313</v>
       </c>
       <c r="E18" t="n">
-        <v>0.896</v>
+        <v>0.9926</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5381</v>
+        <v>-2.2239</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6012</v>
+        <v>-0.5958</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1439</v>
+        <v>-0.1336</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5704</v>
+        <v>1.5483</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8179</v>
+        <v>-0.8348</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1716</v>
+        <v>-2.1441</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5321</v>
+        <v>-2.5168</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7322</v>
+        <v>1.1368</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4597</v>
+        <v>0.5825</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2725</v>
+        <v>0.5543</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0244</v>
+        <v>-1.9857</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5423</v>
+        <v>1.6407</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5667</v>
+        <v>-3.6264</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4986</v>
+        <v>0.4972</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2771</v>
+        <v>-0.2758</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7756</v>
+        <v>0.773</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3075</v>
+        <v>2.289</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8089</v>
+        <v>-1.7918</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.757</v>
+        <v>0.7839</v>
       </c>
       <c r="T19" t="n">
-        <v>0.369</v>
+        <v>0.4899</v>
       </c>
       <c r="U19" t="n">
-        <v>0.388</v>
+        <v>0.294</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.0531</v>
+        <v>-3.0392</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.0531</v>
+        <v>-3.0392</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>D. KRAVISH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0472</v>
+        <v>-2.2435</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2971</v>
+        <v>-1.6795</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3443</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7513</v>
+        <v>-2.4467</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3292</v>
+        <v>0.382</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5779</v>
+        <v>-2.8287</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7543</v>
+        <v>-1.7629</v>
       </c>
       <c r="K20" t="n">
-        <v>3.605</v>
+        <v>-0.2208</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1493</v>
+        <v>-1.542</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.0029</v>
+        <v>-0.6838</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2758</v>
+        <v>0.6028</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7272</v>
+        <v>-1.2866</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.3098</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.7635</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9611</v>
+        <v>0.2031</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6635</v>
+        <v>0.0834</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2976</v>
+        <v>0.1198</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4498</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6429</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. KRAVISH</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1733</v>
+        <v>-2.8297</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3764</v>
+        <v>0.2986</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.797</v>
+        <v>-3.1283</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4484</v>
+        <v>0.7436</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3824</v>
+        <v>2.3102</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8308</v>
+        <v>-1.5666</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7503</v>
+        <v>3.7235</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2149</v>
+        <v>3.5745</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5354</v>
+        <v>0.1489</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-2.9799</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5973000000000001</v>
+        <v>-1.2643</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2954</v>
+        <v>-1.7155</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-4.325</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-4.7803</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.725</v>
+        <v>1.2101</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6261</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0989</v>
+        <v>0.4857</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.4584</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6311</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6329</v>
+        <v>-3.2355</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.991</v>
+        <v>-2.3085</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.642</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4957</v>
+        <v>-2.4899</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5598</v>
+        <v>-2.5618</v>
       </c>
       <c r="I22" t="n">
-        <v>0.064</v>
+        <v>0.0718</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9428</v>
+        <v>-0.9575</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6145</v>
+        <v>-1.6277</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.553</v>
+        <v>-1.5325</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4506</v>
+        <v>0.8479</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4869</v>
+        <v>0.2228</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9376</v>
+        <v>0.6251</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2157</v>
+        <v>-6.3859</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9298</v>
+        <v>-3.9079</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.286</v>
+        <v>-2.478</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.5563</v>
+        <v>-7.5635</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.948</v>
+        <v>-1.9473</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.6083</v>
+        <v>-5.6162</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.6411</v>
+        <v>-4.6719</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9781</v>
+        <v>-1.9897</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.663</v>
+        <v>-2.6822</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9152</v>
+        <v>-2.8916</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.9453</v>
+        <v>-2.934</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6179</v>
+        <v>0.2263</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.113</v>
+        <v>-0.0492</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4951</v>
+        <v>0.2755</v>
       </c>
       <c r="V23" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.2514</v>
+        <v>-15.2471</v>
       </c>
       <c r="E24" t="n">
-        <v>2.897499999999999</v>
+        <v>2.631199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.1491</v>
+        <v>-17.8784</v>
       </c>
       <c r="G24" t="n">
-        <v>-14.1019</v>
+        <v>-14.1132</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.6934</v>
+        <v>-3.7317</v>
       </c>
       <c r="I24" t="n">
-        <v>-10.4089</v>
+        <v>-10.3815</v>
       </c>
       <c r="J24" t="n">
-        <v>4.641500000000001</v>
+        <v>4.421900000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.06280000000000019</v>
+        <v>-0.2073</v>
       </c>
       <c r="L24" t="n">
-        <v>4.704099999999999</v>
+        <v>4.629500000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-18.7435</v>
+        <v>-18.535</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.6307</v>
+        <v>-3.5241</v>
       </c>
       <c r="O24" t="n">
-        <v>-15.1128</v>
+        <v>-15.0107</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.6707</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q24" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R24" t="n">
-        <v>6.805000000000001</v>
+        <v>6.829</v>
       </c>
       <c r="S24" t="n">
-        <v>7.863499999999999</v>
+        <v>7.8963</v>
       </c>
       <c r="T24" t="n">
-        <v>4.1435</v>
+        <v>4.1775</v>
       </c>
       <c r="U24" t="n">
-        <v>3.72</v>
+        <v>3.718900000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.3423</v>
+        <v>-3.3399</v>
       </c>
       <c r="W24" t="n">
-        <v>6.5884</v>
+        <v>6.5517</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.9307</v>
+        <v>-9.891600000000002</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104488_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104488_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3757</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.0804</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.2465</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.23</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.7747</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0782</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.5518</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-3.0392</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104488_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.891600000000002</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
